--- a/output/pdf_financials_xlsx/YARR.xlsx
+++ b/output/pdf_financials_xlsx/YARR.xlsx
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.52207</v>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.52207</v>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.52207</v>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.52207</v>
@@ -1742,16 +1742,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.52207</v>
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5645,16 +5645,16 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014855</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.0065</v>
+        <v>-0.015</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.289405</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -12800,7 +12800,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -20453,10 +20457,10 @@
         </is>
       </c>
       <c r="H195" s="5" t="n">
-        <v>0.367309</v>
+        <v>-0.367309</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.52207</v>
+        <v>-0.52207</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -20948,16 +20952,16 @@
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.451865</v>
+        <v>-0.451865</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.124758</v>
+        <v>-0.124758</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>0.172949</v>
+        <v>-0.172949</v>
       </c>
       <c r="H202" s="5" t="n">
-        <v>0.207107</v>
+        <v>-0.207107</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/YARR.xlsx
+++ b/output/pdf_financials_xlsx/YARR.xlsx
@@ -804,13 +804,13 @@
         <v>0.084971</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.029721</v>
+        <v>0.124758</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.02514</v>
+        <v>0.172949</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.051049</v>
+        <v>0.207107</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.08448</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.051049</v>
+        <v>-0.207107</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-0.536557</v>
@@ -906,19 +906,19 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.015372</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.034499</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.013091</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.04961</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.109915</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0.072867</v>
@@ -1671,19 +1671,19 @@
         <v>-0.52207</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.480647</v>
+        <v>-3.496019</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.475154</v>
+        <v>-2.509653</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.7744</v>
+        <v>-3.787491</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-12.264912</v>
+        <v>-12.314522</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.939574</v>
+        <v>-10.049489</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.115561</v>
@@ -1757,19 +1757,19 @@
         <v>-0.52207</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.480647</v>
+        <v>-3.496019</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.475154</v>
+        <v>-2.509653</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.7744</v>
+        <v>-3.787491</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-12.264912</v>
+        <v>-12.314522</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.939574</v>
+        <v>-10.049489</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.115561</v>
@@ -1969,16 +1969,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055495</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.040686</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.012409</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.203448</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.556021</v>
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055495</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.040686</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.012409</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.203448</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.556021</v>
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.08759699999999999</v>
+        <v>0.032102</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.040686</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.012409</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.209948</v>
+        <v>0.0065</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.007922</v>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">

--- a/output/pdf_financials_xlsx/YARR.xlsx
+++ b/output/pdf_financials_xlsx/YARR.xlsx
@@ -5393,19 +5393,19 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -11026,7 +11026,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/YARR.xlsx
+++ b/output/pdf_financials_xlsx/YARR.xlsx
@@ -693,19 +693,19 @@
         <v>0.099885</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.130211</v>
+        <v>0.162011</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.229192</v>
+        <v>0.260092</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.233974</v>
+        <v>0.266148</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.219348</v>
+        <v>0.249048</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.255507</v>
+        <v>0.287607</v>
       </c>
     </row>
     <row r="8">
@@ -822,19 +822,19 @@
         <v>0.192392</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.217789</v>
+        <v>0.249589</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.421961</v>
+        <v>0.452861</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.456636</v>
+        <v>0.48881</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.297926</v>
+        <v>0.327626</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.330368</v>
+        <v>0.362468</v>
       </c>
     </row>
     <row r="11">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.007853000000000001</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.004412</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.003791</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.016905</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.018297</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -3412,19 +3412,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.039457</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.057451</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.053454</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.054154</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.041839</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -4902,19 +4902,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.003412</v>
+        <v>0.039568</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.018491</v>
+        <v>0.008044000000000001</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.013457</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-4.9e-05</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.002811</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.214078</v>
@@ -5117,19 +5117,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.032618</v>
+        <v>0.010362</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.033044</v>
+        <v>0.022597</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.004618</v>
+        <v>0.008839</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.016254</v>
+        <v>0.016205</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.012682</v>
+        <v>-0.009871</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.355142</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.088965</v>
       </c>
     </row>
     <row r="116">
@@ -11100,7 +11100,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -12148,7 +12152,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -12958,7 +12966,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -13626,7 +13638,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -15052,7 +15068,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>0.04298</v>
       </c>
@@ -16024,7 +16044,11 @@
           <t>Proceeds from issuance of shares in private placement</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>0.043</v>
       </c>
@@ -16594,7 +16618,11 @@
           <t>Directors fees (note 11)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -18096,7 +18124,11 @@
           <t>Directors fees (note 10)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
